--- a/Practice Excel Sheets/Lesson 8-Filter Data in Excel/8-Excel-Filter Data in Excel.xlsx
+++ b/Practice Excel Sheets/Lesson 8-Filter Data in Excel/8-Excel-Filter Data in Excel.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30030"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CHANNELS\Satish Dhawale\Excel Beginners to Advance\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YUVRAJ\Desktop\My Activities\GitHub\Excel\Practice Excel Sheets\Lesson 8-Filter Data in Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F956036-B6B2-4DA2-AFBF-AA6A163D9FB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Employee Data" sheetId="1" r:id="rId1"/>
@@ -380,7 +380,7 @@
 </file>
 
 <file path=xl/activeX/activeX1.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{D7053240-CE69-11CD-A777-00DD01143C57}" ax:persistence="persistStreamInit" r:id="rId1"/>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{8BD21D30-EC42-11CE-9E0D-00AA006002F3}" ax:persistence="persistStreamInit" r:id="rId1"/>
 </file>
 
 <file path=xl/activeX/activeX2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -388,7 +388,7 @@
 </file>
 
 <file path=xl/activeX/activeX3.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{8BD21D30-EC42-11CE-9E0D-00AA006002F3}" ax:persistence="persistStreamInit" r:id="rId1"/>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{D7053240-CE69-11CD-A777-00DD01143C57}" ax:persistence="persistStreamInit" r:id="rId1"/>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -416,7 +416,7 @@
                   <a14:compatExt spid="_x0000_s7169"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A863F870-9D86-82C4-3708-CCF18271C231}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000011C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -436,27 +436,16 @@
             <a:ln>
               <a:noFill/>
             </a:ln>
-            <a:effectLst/>
             <a:extLst>
               <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
                 <a14:hiddenLine w="9525">
                   <a:solidFill>
                     <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
                   </a:solidFill>
-                  <a:prstDash val="solid"/>
                   <a:miter lim="800000"/>
                   <a:headEnd/>
-                  <a:tailEnd type="none" w="med" len="med"/>
+                  <a:tailEnd/>
                 </a14:hiddenLine>
-              </a:ext>
-              <a:ext uri="{AF507438-7753-43E0-B8FC-AC1667EBCBE1}">
-                <a14:hiddenEffects>
-                  <a:effectLst>
-                    <a:outerShdw dist="35921" dir="2700000" algn="ctr" rotWithShape="0">
-                      <a:srgbClr val="808080"/>
-                    </a:outerShdw>
-                  </a:effectLst>
-                </a14:hiddenEffects>
               </a:ext>
             </a:extLst>
           </xdr:spPr>
@@ -489,7 +478,7 @@
                   <a14:compatExt spid="_x0000_s7170"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1B9FD6D8-4EA1-671B-45B9-CD80BA652D5D}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000021C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -509,27 +498,16 @@
             <a:ln>
               <a:noFill/>
             </a:ln>
-            <a:effectLst/>
             <a:extLst>
               <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
                 <a14:hiddenLine w="9525">
                   <a:solidFill>
                     <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
                   </a:solidFill>
-                  <a:prstDash val="solid"/>
                   <a:miter lim="800000"/>
                   <a:headEnd/>
-                  <a:tailEnd type="none" w="med" len="med"/>
+                  <a:tailEnd/>
                 </a14:hiddenLine>
-              </a:ext>
-              <a:ext uri="{AF507438-7753-43E0-B8FC-AC1667EBCBE1}">
-                <a14:hiddenEffects>
-                  <a:effectLst>
-                    <a:outerShdw dist="35921" dir="2700000" algn="ctr" rotWithShape="0">
-                      <a:srgbClr val="808080"/>
-                    </a:outerShdw>
-                  </a:effectLst>
-                </a14:hiddenEffects>
               </a:ext>
             </a:extLst>
           </xdr:spPr>
@@ -562,7 +540,7 @@
                   <a14:compatExt spid="_x0000_s7171"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{011541A2-E7D2-CA56-A496-DB1E4C4BE639}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000031C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -582,27 +560,16 @@
             <a:ln>
               <a:noFill/>
             </a:ln>
-            <a:effectLst/>
             <a:extLst>
               <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
                 <a14:hiddenLine w="9525">
                   <a:solidFill>
                     <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
                   </a:solidFill>
-                  <a:prstDash val="solid"/>
                   <a:miter lim="800000"/>
                   <a:headEnd/>
-                  <a:tailEnd type="none" w="med" len="med"/>
+                  <a:tailEnd/>
                 </a14:hiddenLine>
-              </a:ext>
-              <a:ext uri="{AF507438-7753-43E0-B8FC-AC1667EBCBE1}">
-                <a14:hiddenEffects>
-                  <a:effectLst>
-                    <a:outerShdw dist="35921" dir="2700000" algn="ctr" rotWithShape="0">
-                      <a:srgbClr val="808080"/>
-                    </a:outerShdw>
-                  </a:effectLst>
-                </a14:hiddenEffects>
               </a:ext>
             </a:extLst>
           </xdr:spPr>
@@ -10168,27 +10135,27 @@
   <controls>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="7171" r:id="rId3" name="btnXLExport_224818">
+        <control shapeId="7169" r:id="rId3" name="cmbXLGroupBy_224818">
           <controlPr defaultSize="0" autoLine="0" r:id="rId4">
             <anchor moveWithCells="1">
               <from>
-                <xdr:col>6</xdr:col>
-                <xdr:colOff>723900</xdr:colOff>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>22860</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>76200</xdr:rowOff>
               </from>
               <to>
-                <xdr:col>9</xdr:col>
-                <xdr:colOff>365760</xdr:colOff>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>259080</xdr:colOff>
                 <xdr:row>2</xdr:row>
-                <xdr:rowOff>381000</xdr:rowOff>
+                <xdr:rowOff>350520</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="7171" r:id="rId3" name="btnXLExport_224818"/>
+        <control shapeId="7169" r:id="rId3" name="cmbXLGroupBy_224818"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -10218,27 +10185,27 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="7169" r:id="rId7" name="cmbXLGroupBy_224818">
+        <control shapeId="7171" r:id="rId7" name="btnXLExport_224818">
           <controlPr defaultSize="0" autoLine="0" r:id="rId8">
             <anchor moveWithCells="1">
               <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>22860</xdr:colOff>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>723900</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>76200</xdr:rowOff>
               </from>
               <to>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>259080</xdr:colOff>
+                <xdr:col>9</xdr:col>
+                <xdr:colOff>365760</xdr:colOff>
                 <xdr:row>2</xdr:row>
-                <xdr:rowOff>350520</xdr:rowOff>
+                <xdr:rowOff>381000</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="7169" r:id="rId7" name="cmbXLGroupBy_224818"/>
+        <control shapeId="7171" r:id="rId7" name="btnXLExport_224818"/>
       </mc:Fallback>
     </mc:AlternateContent>
   </controls>
